--- a/04_Figures/F06_prediction/modules/T1/ridge/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/T1/ridge/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -171,12 +171,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -569,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -602,7 +596,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
@@ -614,16 +608,16 @@
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.174129353233831</v>
+        <v>0.149253731343284</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.153174928750372</v>
+        <v>-0.160404044312035</v>
       </c>
       <c r="M3" t="n">
-        <v>0.157491458981609</v>
+        <v>0.121167420208204</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +637,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -676,7 +670,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
@@ -688,16 +682,16 @@
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.502487562189055</v>
+        <v>0.477611940298507</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.186965833818011</v>
+        <v>-0.179538504404569</v>
       </c>
       <c r="M5" t="n">
-        <v>0.163945570852453</v>
+        <v>0.147585885614634</v>
       </c>
     </row>
     <row r="6">
@@ -717,7 +711,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -750,7 +744,7 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
@@ -762,16 +756,16 @@
         <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.611940298507463</v>
+        <v>0.686567164179104</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.199392032066795</v>
+        <v>-0.179546451996942</v>
       </c>
       <c r="M7" t="n">
-        <v>0.199460989893894</v>
+        <v>0.14428012899602</v>
       </c>
     </row>
     <row r="8">
@@ -791,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -824,7 +818,7 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
@@ -836,16 +830,16 @@
         <v>-1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.402985074626866</v>
+        <v>0.427860696517413</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.171228511764858</v>
+        <v>-0.159229784891716</v>
       </c>
       <c r="M9" t="n">
-        <v>0.155758587970544</v>
+        <v>0.100162737036385</v>
       </c>
     </row>
     <row r="10">
@@ -865,7 +859,7 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -898,7 +892,7 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
@@ -910,16 +904,16 @@
         <v>-1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.358208955223881</v>
+        <v>0.338308457711443</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.182831623327534</v>
+        <v>-0.181460641341446</v>
       </c>
       <c r="M11" t="n">
-        <v>0.127201073070999</v>
+        <v>0.103093506605819</v>
       </c>
     </row>
     <row r="12">
@@ -939,16 +933,16 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.161542545218869</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.998898071290657</v>
+        <v>-0.932745881138958</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -972,28 +966,28 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.161542545218869</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.998898071290657</v>
+        <v>-0.932745881138958</v>
       </c>
       <c r="J13" t="n">
-        <v>0.920398009950249</v>
+        <v>0.651741293532338</v>
       </c>
       <c r="K13" t="n">
-        <v>0.442786069651741</v>
+        <v>0.159203980099502</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.16049466907133</v>
+        <v>-0.194656579512579</v>
       </c>
       <c r="M13" t="n">
-        <v>0.00392326564865378</v>
+        <v>0.0975824194782344</v>
       </c>
     </row>
   </sheetData>
@@ -1048,7 +1042,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.152575403131063</v>
+        <v>-0.178708981613099</v>
       </c>
     </row>
     <row r="5">
@@ -1059,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.19165991372711</v>
+        <v>-0.219346010203815</v>
       </c>
     </row>
     <row r="6">
@@ -1070,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>0.322347972291345</v>
+        <v>-0.210763848087732</v>
       </c>
     </row>
     <row r="7">
@@ -1103,7 +1097,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>0.392776498689206</v>
+        <v>-0.276017110958127</v>
       </c>
     </row>
     <row r="10">
@@ -1125,7 +1119,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.156184199922085</v>
+        <v>-0.272296797355941</v>
       </c>
     </row>
     <row r="12">
@@ -1180,7 +1174,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.292455672778277</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="17">
@@ -1224,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.376773157636471</v>
+        <v>-0.324171001736877</v>
       </c>
     </row>
     <row r="21">
@@ -1246,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.216338920383834</v>
+        <v>-0.196118296817326</v>
       </c>
     </row>
     <row r="23">
@@ -1268,7 +1262,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.171966907785105</v>
       </c>
     </row>
     <row r="25">
@@ -1290,7 +1284,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>0.10712005593209</v>
+        <v>0.1574383191546</v>
       </c>
     </row>
     <row r="27">
@@ -1356,7 +1350,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>0.091188091690798</v>
+        <v>0.141179033750703</v>
       </c>
     </row>
     <row r="33">
@@ -1378,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.271929013141977</v>
+        <v>-0.231219622767016</v>
       </c>
     </row>
     <row r="35">
@@ -1400,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.220184666820934</v>
       </c>
     </row>
     <row r="37">
@@ -1411,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.194020989866204</v>
+        <v>-0.298924285265735</v>
       </c>
     </row>
     <row r="38">
@@ -1444,7 +1438,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.427084648022422</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="41">
@@ -1477,7 +1471,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.356905633259893</v>
+        <v>-0.426986037658894</v>
       </c>
     </row>
     <row r="44">
@@ -1499,7 +1493,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>0.219236355347677</v>
+        <v>0.338509653647404</v>
       </c>
     </row>
     <row r="46">
@@ -1510,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.356811931762612</v>
+        <v>-0.266746591295355</v>
       </c>
     </row>
     <row r="47">
@@ -1521,7 +1515,7 @@
         <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.199541369420807</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="48">
@@ -1532,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.183454017972999</v>
+        <v>-0.194732737687498</v>
       </c>
     </row>
     <row r="49">
@@ -1543,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.23861890959492</v>
+        <v>-0.304296131881933</v>
       </c>
     </row>
     <row r="50">
@@ -1554,7 +1548,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.023018340692903</v>
+        <v>-0.0510669029667801</v>
       </c>
     </row>
     <row r="51">
@@ -1565,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.191534389560714</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="52">
@@ -1576,7 +1570,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.221979135276806</v>
+        <v>-0.163260956614663</v>
       </c>
     </row>
     <row r="53">
@@ -1609,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.279612779771015</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="56">
@@ -1620,7 +1614,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.150277435712538</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="57">
@@ -1631,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.25425626288005</v>
+        <v>-0.356074623475948</v>
       </c>
     </row>
     <row r="58">
@@ -1642,7 +1636,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.242150672004206</v>
+        <v>-0.409978007764311</v>
       </c>
     </row>
     <row r="59">
@@ -1686,7 +1680,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.267904226657238</v>
+        <v>-0.163228754303113</v>
       </c>
     </row>
     <row r="63">
@@ -1697,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.440351025904591</v>
+        <v>-0.197838728422198</v>
       </c>
     </row>
     <row r="64">
@@ -1708,7 +1702,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.223885649865666</v>
       </c>
     </row>
     <row r="65">
@@ -1730,7 +1724,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.293754851733818</v>
+        <v>-0.292394362107821</v>
       </c>
     </row>
     <row r="67">
@@ -1774,7 +1768,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.158598317760889</v>
+        <v>-0.149880069034256</v>
       </c>
     </row>
     <row r="71">
@@ -1796,7 +1790,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.188232350703639</v>
+        <v>-0.210742653071078</v>
       </c>
     </row>
     <row r="73">
@@ -1807,7 +1801,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.20709898063102</v>
+        <v>-0.188541009519211</v>
       </c>
     </row>
     <row r="74">
@@ -1818,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.16248743954175</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="75">
@@ -1829,7 +1823,7 @@
         <v>16</v>
       </c>
       <c r="C75" t="n">
-        <v>0.495334615417518</v>
+        <v>-0.245092648519703</v>
       </c>
     </row>
     <row r="76">
@@ -1873,7 +1867,7 @@
         <v>16</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.173300901842873</v>
+        <v>-0.183157086381124</v>
       </c>
     </row>
     <row r="80">
@@ -1895,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>0.393438823592379</v>
+        <v>0.348217327729524</v>
       </c>
     </row>
     <row r="82">
@@ -1906,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.251386704203265</v>
+        <v>-0.259384503658053</v>
       </c>
     </row>
     <row r="83">
@@ -1917,7 +1911,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.176304339000192</v>
+        <v>-0.199822632397336</v>
       </c>
     </row>
     <row r="84">
@@ -1939,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.193908284244597</v>
+        <v>-0.39838067147519</v>
       </c>
     </row>
     <row r="86">
@@ -1950,7 +1944,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0087622735744326</v>
+        <v>0.236739545960874</v>
       </c>
     </row>
     <row r="87">
@@ -1961,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.226934360908553</v>
+        <v>-0.314644281754653</v>
       </c>
     </row>
     <row r="88">
@@ -1972,7 +1966,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.325372769321255</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="89">
@@ -1983,7 +1977,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.232089075739473</v>
+        <v>-0.34820454348789</v>
       </c>
     </row>
     <row r="90">
@@ -1994,7 +1988,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.148078083645682</v>
+        <v>-0.14445815865162</v>
       </c>
     </row>
     <row r="91">
@@ -2016,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.172515411155301</v>
       </c>
     </row>
     <row r="93">
@@ -2027,7 +2021,7 @@
         <v>16</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.0679026816311221</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="94">
@@ -2049,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.428216949006057</v>
+        <v>-0.318472376346201</v>
       </c>
     </row>
     <row r="96">
@@ -2060,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0926467737914628</v>
+        <v>0.12875193531084</v>
       </c>
     </row>
     <row r="97">
@@ -2082,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.341911926528391</v>
+        <v>-0.409140001780083</v>
       </c>
     </row>
     <row r="99">
@@ -2093,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.123464874540006</v>
+        <v>-0.147074211808671</v>
       </c>
     </row>
     <row r="100">
@@ -2104,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>0.213857343046692</v>
+        <v>-0.158507808579754</v>
       </c>
     </row>
     <row r="101">
@@ -2148,7 +2142,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.21331789630647</v>
+        <v>-0.169476423993916</v>
       </c>
     </row>
     <row r="105">
@@ -2159,7 +2153,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.180587671245731</v>
+        <v>-0.201367767075995</v>
       </c>
     </row>
     <row r="106">
@@ -2181,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.215139064528253</v>
+        <v>-0.283371909500725</v>
       </c>
     </row>
     <row r="108">
@@ -2203,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>0.049103685064061</v>
+        <v>0.0792364743970825</v>
       </c>
     </row>
     <row r="110">
@@ -2247,7 +2241,7 @@
         <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.33113071669374</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="114">
@@ -2258,7 +2252,7 @@
         <v>16</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.77861830775327</v>
+        <v>-0.0394739971822313</v>
       </c>
     </row>
     <row r="115">
@@ -2280,7 +2274,7 @@
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.149111215851179</v>
+        <v>-0.21926241593547</v>
       </c>
     </row>
     <row r="117">
@@ -2291,7 +2285,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.264248956840381</v>
       </c>
     </row>
     <row r="118">
@@ -2302,7 +2296,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.372604275776717</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="119">
@@ -2313,7 +2307,7 @@
         <v>16</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.481964528103336</v>
+        <v>-0.286535470309015</v>
       </c>
     </row>
     <row r="120">
@@ -2335,7 +2329,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.0468604948631846</v>
+        <v>-0.00657377889495403</v>
       </c>
     </row>
     <row r="122">
@@ -2379,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.161181379497443</v>
+        <v>-0.274167827717053</v>
       </c>
     </row>
     <row r="126">
@@ -2401,7 +2395,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.221305965619861</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="128">
@@ -2412,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.108010069011343</v>
+        <v>-0.130787016556257</v>
       </c>
     </row>
     <row r="129">
@@ -2423,7 +2417,7 @@
         <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.149733256658732</v>
+        <v>-0.128821965007326</v>
       </c>
     </row>
     <row r="130">
@@ -2434,7 +2428,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.0609772575456049</v>
+        <v>-0.299009523949899</v>
       </c>
     </row>
     <row r="131">
@@ -2445,7 +2439,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.315479675458833</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="132">
@@ -2456,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.24574226813417</v>
+        <v>-0.300597620124089</v>
       </c>
     </row>
     <row r="133">
@@ -2467,7 +2461,7 @@
         <v>16</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.478898592586314</v>
+        <v>-0.522882642461284</v>
       </c>
     </row>
     <row r="134">
@@ -2489,7 +2483,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>0.44798432694617</v>
+        <v>0.411513496824329</v>
       </c>
     </row>
     <row r="136">
@@ -2500,7 +2494,7 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>0.228159527904376</v>
+        <v>-0.177211041304062</v>
       </c>
     </row>
     <row r="137">
@@ -2511,7 +2505,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.296722874775914</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="138">
@@ -2522,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.392234326159878</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="139">
@@ -2544,7 +2538,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.231584332373398</v>
+        <v>-0.167614236495037</v>
       </c>
     </row>
     <row r="141">
@@ -2555,7 +2549,7 @@
         <v>16</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.19374987099028</v>
+        <v>-0.180568306560482</v>
       </c>
     </row>
     <row r="142">
@@ -2588,7 +2582,7 @@
         <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.194950227203984</v>
+        <v>-0.216517848920558</v>
       </c>
     </row>
     <row r="145">
@@ -2599,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.00161748333205991</v>
+        <v>-0.0674188982211452</v>
       </c>
     </row>
     <row r="146">
@@ -2621,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.466589885895256</v>
+        <v>-0.473537931148643</v>
       </c>
     </row>
     <row r="148">
@@ -2654,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.22869248412326</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="151">
@@ -2676,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.167508420151327</v>
+        <v>-0.164226577349085</v>
       </c>
     </row>
     <row r="153">
@@ -2720,7 +2714,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.0071722169483901</v>
+        <v>-0.109216214292254</v>
       </c>
     </row>
     <row r="157">
@@ -2731,7 +2725,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.217545012705722</v>
       </c>
     </row>
     <row r="158">
@@ -2742,7 +2736,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.203835406826148</v>
+        <v>-0.27605444220478</v>
       </c>
     </row>
     <row r="159">
@@ -2753,7 +2747,7 @@
         <v>16</v>
       </c>
       <c r="C159" t="n">
-        <v>0.519742075611325</v>
+        <v>0.344433758427738</v>
       </c>
     </row>
     <row r="160">
@@ -2764,7 +2758,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.274428289835279</v>
+        <v>-0.25521176851371</v>
       </c>
     </row>
     <row r="161">
@@ -2775,7 +2769,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.208177985376425</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="162">
@@ -2786,7 +2780,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.342410600981626</v>
+        <v>0.0436360095966096</v>
       </c>
     </row>
     <row r="163">
@@ -2797,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.201631528900339</v>
+        <v>-0.150834620341427</v>
       </c>
     </row>
     <row r="164">
@@ -2808,7 +2802,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.133461738200507</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="165">
@@ -2819,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.16845136202709</v>
+        <v>-0.10661810018239</v>
       </c>
     </row>
     <row r="166">
@@ -2874,7 +2868,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.326087474962493</v>
+        <v>-0.249042886449227</v>
       </c>
     </row>
     <row r="171">
@@ -2907,7 +2901,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.286396015603091</v>
       </c>
     </row>
     <row r="174">
@@ -2918,7 +2912,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.271540077394272</v>
       </c>
     </row>
     <row r="175">
@@ -2929,7 +2923,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.229379921469493</v>
+        <v>-0.265152966930494</v>
       </c>
     </row>
     <row r="176">
@@ -2940,7 +2934,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.421975882659324</v>
+        <v>-0.248950947547933</v>
       </c>
     </row>
     <row r="177">
@@ -2973,7 +2967,7 @@
         <v>16</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.162476150967509</v>
+        <v>-0.257847739698867</v>
       </c>
     </row>
     <row r="180">
@@ -2984,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>0.278420288304114</v>
+        <v>-0.0966053965051177</v>
       </c>
     </row>
     <row r="181">
@@ -2995,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.204045586498299</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="182">
@@ -3006,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.0521990070420195</v>
+        <v>-0.187498178853764</v>
       </c>
     </row>
     <row r="183">
@@ -3017,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.163980637840496</v>
+        <v>-0.279726354936619</v>
       </c>
     </row>
     <row r="184">
@@ -3039,7 +3033,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.1647333024623</v>
       </c>
     </row>
     <row r="186">
@@ -3050,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.345274693343492</v>
+        <v>-0.222658761059524</v>
       </c>
     </row>
     <row r="187">
@@ -3061,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.149696843897155</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="188">
@@ -3083,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.260733855421629</v>
+        <v>-0.21061967480397</v>
       </c>
     </row>
     <row r="190">
@@ -3105,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.169470160642614</v>
+        <v>-0.147050011095067</v>
       </c>
     </row>
     <row r="192">
@@ -3116,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.148934537357889</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="193">
@@ -3127,7 +3121,7 @@
         <v>16</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.348909680876912</v>
+        <v>-0.32646550109427</v>
       </c>
     </row>
     <row r="194">
@@ -3149,7 +3143,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>0.058397398303048</v>
+        <v>0.270112982624926</v>
       </c>
     </row>
     <row r="196">
@@ -3171,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.0620657085455163</v>
+        <v>-0.25757351631918</v>
       </c>
     </row>
     <row r="198">
@@ -3215,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="C201" t="n">
-        <v>0.156213344722055</v>
+        <v>-0.0897060211527625</v>
       </c>
     </row>
     <row r="202">
@@ -3248,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.244207717208699</v>
+        <v>-0.205850941749253</v>
       </c>
     </row>
     <row r="205">
@@ -3270,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.198140412574028</v>
+        <v>-0.0156099822866169</v>
       </c>
     </row>
     <row r="207">
@@ -3303,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.392928487652437</v>
+        <v>-0.280206000573096</v>
       </c>
     </row>
     <row r="210">
@@ -3325,7 +3319,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.373807797542389</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="212">
@@ -3336,7 +3330,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.329604948234019</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="213">
@@ -3358,7 +3352,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.173292048379425</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="215">
@@ -3380,7 +3374,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.573743861529058</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="217">
@@ -3391,7 +3385,7 @@
         <v>16</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.187610481238315</v>
       </c>
     </row>
     <row r="218">
@@ -3413,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.231402609155526</v>
       </c>
     </row>
     <row r="220">
@@ -3424,7 +3418,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>0.0968482304920677</v>
+        <v>-0.112850468718144</v>
       </c>
     </row>
     <row r="221">
@@ -3490,7 +3484,7 @@
         <v>16</v>
       </c>
       <c r="C226" t="n">
-        <v>0.0264928767840024</v>
+        <v>-0.145097592051118</v>
       </c>
     </row>
     <row r="227">
@@ -3523,7 +3517,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.191267763958389</v>
+        <v>-0.130690517450316</v>
       </c>
     </row>
     <row r="230">
@@ -3556,7 +3550,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.219349730896912</v>
+        <v>-0.220409425067618</v>
       </c>
     </row>
     <row r="233">
@@ -3578,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.174132662688735</v>
+        <v>-0.183851967375565</v>
       </c>
     </row>
     <row r="235">
@@ -3600,7 +3594,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.150195123131073</v>
       </c>
     </row>
     <row r="237">
@@ -3611,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>0.0650481878726857</v>
+        <v>-0.333042929520496</v>
       </c>
     </row>
     <row r="238">
@@ -3644,7 +3638,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.363431327088265</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="241">
@@ -3666,7 +3660,7 @@
         <v>16</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.148255092121347</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="243">
@@ -3677,7 +3671,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.4641349090429</v>
+        <v>-0.308295795207102</v>
       </c>
     </row>
     <row r="244">
@@ -3710,7 +3704,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.310635993694457</v>
+        <v>-0.361135806785063</v>
       </c>
     </row>
     <row r="247">
@@ -3732,7 +3726,7 @@
         <v>16</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.141682056677474</v>
+        <v>-0.174355992194339</v>
       </c>
     </row>
     <row r="249">
@@ -3743,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.305242887649276</v>
       </c>
     </row>
     <row r="250">
@@ -3776,7 +3770,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.18345939434758</v>
+        <v>-0.163629277981357</v>
       </c>
     </row>
     <row r="253">
@@ -3787,7 +3781,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.194672197521393</v>
+        <v>-0.18894755297429</v>
       </c>
     </row>
     <row r="254">
@@ -3798,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.430556265268734</v>
       </c>
     </row>
     <row r="255">
@@ -3820,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.322125092623101</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="257">
@@ -3831,7 +3825,7 @@
         <v>16</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.232382506779458</v>
+        <v>-0.435909688650452</v>
       </c>
     </row>
     <row r="258">
@@ -3842,7 +3836,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.152553869290191</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="259">
@@ -3864,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.150100930230261</v>
       </c>
     </row>
     <row r="261">
@@ -3897,7 +3891,7 @@
         <v>16</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.483230519377946</v>
+        <v>-0.215696829702246</v>
       </c>
     </row>
     <row r="264">
@@ -3930,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.250044005305171</v>
+        <v>-0.209853959046895</v>
       </c>
     </row>
     <row r="267">
@@ -3941,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.440836459274153</v>
+        <v>-0.776025487765153</v>
       </c>
     </row>
     <row r="268">
@@ -3952,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.445806998281561</v>
+        <v>-0.238714011420775</v>
       </c>
     </row>
     <row r="269">
@@ -3963,7 +3957,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.373241667161154</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="270">
@@ -3974,7 +3968,7 @@
         <v>16</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.189666219242361</v>
+        <v>-0.174690628503462</v>
       </c>
     </row>
     <row r="271">
@@ -3985,7 +3979,7 @@
         <v>16</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.738466843355206</v>
+        <v>-0.965509782124222</v>
       </c>
     </row>
     <row r="272">
@@ -4007,7 +4001,7 @@
         <v>16</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.195868863857749</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="274">
@@ -4018,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.318292285360481</v>
+        <v>-0.250871932342589</v>
       </c>
     </row>
     <row r="275">
@@ -4029,7 +4023,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.13062969590791</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="276">
@@ -4073,7 +4067,7 @@
         <v>16</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.316184429956726</v>
+        <v>-0.21779477859208</v>
       </c>
     </row>
     <row r="280">
@@ -4095,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>0.0858502727063516</v>
+        <v>-0.115321250738001</v>
       </c>
     </row>
     <row r="282">
@@ -4106,7 +4100,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.161127817658285</v>
+        <v>0.39933516657305</v>
       </c>
     </row>
     <row r="283">
@@ -4128,7 +4122,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.310164921978872</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="285">
@@ -4139,7 +4133,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.167535924559129</v>
       </c>
     </row>
     <row r="286">
@@ -4150,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.165579342477108</v>
+        <v>-0.067935163761565</v>
       </c>
     </row>
     <row r="287">
@@ -4161,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.370875927892757</v>
+        <v>-0.282392152788901</v>
       </c>
     </row>
     <row r="288">
@@ -4183,7 +4177,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.133752285595401</v>
+        <v>-0.117649380270491</v>
       </c>
     </row>
     <row r="290">
@@ -4194,7 +4188,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.00332046628278104</v>
+        <v>0.145790332770208</v>
       </c>
     </row>
     <row r="291">
@@ -4227,7 +4221,7 @@
         <v>16</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.217484320256641</v>
+        <v>-0.179009020337938</v>
       </c>
     </row>
     <row r="294">
@@ -4249,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.367832834987786</v>
+        <v>-0.338059102674032</v>
       </c>
     </row>
     <row r="296">
@@ -4260,7 +4254,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>0.082106296012933</v>
+        <v>0.223913238075351</v>
       </c>
     </row>
     <row r="297">
@@ -4282,7 +4276,7 @@
         <v>16</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.203237204937818</v>
       </c>
     </row>
     <row r="299">
@@ -4293,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>0.309393562461582</v>
+        <v>0.0448240064753938</v>
       </c>
     </row>
     <row r="300">
@@ -4304,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>0.146284276212993</v>
+        <v>-0.102404453968098</v>
       </c>
     </row>
     <row r="301">
@@ -4348,7 +4342,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.19661857329577</v>
+        <v>-0.225263179202198</v>
       </c>
     </row>
     <row r="305">
@@ -4359,7 +4353,7 @@
         <v>16</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.143196827255612</v>
+        <v>-0.173642400319401</v>
       </c>
     </row>
     <row r="306">
@@ -4403,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.472031058897452</v>
+        <v>-0.158129611288134</v>
       </c>
     </row>
     <row r="310">
@@ -4436,7 +4430,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.182022478001021</v>
       </c>
     </row>
     <row r="313">
@@ -4447,7 +4441,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.159809928837029</v>
+        <v>-0.165503661521522</v>
       </c>
     </row>
     <row r="314">
@@ -4469,7 +4463,7 @@
         <v>16</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.518666373083943</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="316">
@@ -4480,7 +4474,7 @@
         <v>16</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.147084466907747</v>
+        <v>-0.161709666751361</v>
       </c>
     </row>
     <row r="317">
@@ -4491,7 +4485,7 @@
         <v>16</v>
       </c>
       <c r="C317" t="n">
-        <v>-0.272742077787153</v>
+        <v>-0.241117860793567</v>
       </c>
     </row>
     <row r="318">
@@ -4513,7 +4507,7 @@
         <v>16</v>
       </c>
       <c r="C319" t="n">
-        <v>-0.763479362014793</v>
+        <v>-0.565804887511377</v>
       </c>
     </row>
     <row r="320">
@@ -4535,7 +4529,7 @@
         <v>16</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.170283416967338</v>
       </c>
     </row>
     <row r="322">
@@ -4568,7 +4562,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.521261206792718</v>
+        <v>-0.610292891436707</v>
       </c>
     </row>
     <row r="325">
@@ -4579,7 +4573,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.158661598881234</v>
       </c>
     </row>
     <row r="326">
@@ -4601,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.257701000712016</v>
+        <v>-0.28747479599249</v>
       </c>
     </row>
     <row r="328">
@@ -4612,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.0877356136505048</v>
+        <v>-0.224259697846859</v>
       </c>
     </row>
     <row r="329">
@@ -4623,7 +4617,7 @@
         <v>16</v>
       </c>
       <c r="C329" t="n">
-        <v>-0.199248124018827</v>
+        <v>-0.290393234073158</v>
       </c>
     </row>
     <row r="330">
@@ -4634,7 +4628,7 @@
         <v>16</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.276529222637494</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="331">
@@ -4645,7 +4639,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.256598848607831</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="332">
@@ -4656,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.491775706809856</v>
+        <v>-0.421012812920791</v>
       </c>
     </row>
     <row r="333">
@@ -4667,7 +4661,7 @@
         <v>16</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.357709122185767</v>
       </c>
     </row>
     <row r="334">
@@ -4689,7 +4683,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.26887236333353</v>
+        <v>-0.259400648775097</v>
       </c>
     </row>
     <row r="336">
@@ -4700,7 +4694,7 @@
         <v>16</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.199360655431619</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="337">
@@ -4722,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.213410645427504</v>
+        <v>-0.112300500078688</v>
       </c>
     </row>
     <row r="339">
@@ -4744,7 +4738,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.0947796819493705</v>
+        <v>-0.163999214018708</v>
       </c>
     </row>
     <row r="341">
@@ -4755,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.166840098597483</v>
+        <v>-0.215267302243305</v>
       </c>
     </row>
     <row r="342">
@@ -4777,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.482446685850309</v>
+        <v>-0.431152408024332</v>
       </c>
     </row>
     <row r="344">
@@ -4788,7 +4782,7 @@
         <v>16</v>
       </c>
       <c r="C344" t="n">
-        <v>0.277159438199978</v>
+        <v>0.324911242978332</v>
       </c>
     </row>
     <row r="345">
@@ -4799,7 +4793,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.279808532699357</v>
+        <v>-0.333447181501475</v>
       </c>
     </row>
     <row r="346">
@@ -4876,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.0924044312186445</v>
+        <v>-0.0241473318384196</v>
       </c>
     </row>
     <row r="353">
@@ -4887,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.268213711320816</v>
       </c>
     </row>
     <row r="354">
@@ -4920,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>0.302267126127619</v>
+        <v>0.11475384266227</v>
       </c>
     </row>
     <row r="357">
@@ -4931,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.20542806209002</v>
+        <v>-0.20778488812174</v>
       </c>
     </row>
     <row r="358">
@@ -4942,7 +4936,7 @@
         <v>16</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.159286424006813</v>
+        <v>-0.265034095460466</v>
       </c>
     </row>
     <row r="359">
@@ -4953,7 +4947,7 @@
         <v>16</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.225081193235287</v>
+        <v>-0.16862714920364</v>
       </c>
     </row>
     <row r="360">
@@ -4975,7 +4969,7 @@
         <v>16</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.164367839455923</v>
+        <v>-0.216437472922413</v>
       </c>
     </row>
     <row r="362">
@@ -4986,7 +4980,7 @@
         <v>16</v>
       </c>
       <c r="C362" t="n">
-        <v>-0.307369066287054</v>
+        <v>-0.349200468312837</v>
       </c>
     </row>
     <row r="363">
@@ -4997,7 +4991,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.155620137620909</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="364">
@@ -5019,7 +5013,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.303429910878049</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="366">
@@ -5074,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.410898412897413</v>
+        <v>-0.4316514462962</v>
       </c>
     </row>
     <row r="371">
@@ -5085,7 +5079,7 @@
         <v>16</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.266930773963067</v>
       </c>
     </row>
     <row r="372">
@@ -5107,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.287381011289496</v>
       </c>
     </row>
     <row r="374">
@@ -5118,7 +5112,7 @@
         <v>16</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.148862701322033</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="375">
@@ -5129,7 +5123,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>-0.259395895084691</v>
+        <v>-0.175365900384258</v>
       </c>
     </row>
     <row r="376">
@@ -5140,7 +5134,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.290046713798613</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="377">
@@ -5162,7 +5156,7 @@
         <v>16</v>
       </c>
       <c r="C378" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.30917481316891</v>
       </c>
     </row>
     <row r="379">
@@ -5173,7 +5167,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.178490978083915</v>
       </c>
     </row>
     <row r="380">
@@ -5184,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.159985771275271</v>
+        <v>-0.167217743038444</v>
       </c>
     </row>
     <row r="381">
@@ -5250,7 +5244,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.47717766648944</v>
+        <v>-0.596308140265041</v>
       </c>
     </row>
     <row r="387">
@@ -5283,7 +5277,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.297241766159308</v>
+        <v>-0.40304857315202</v>
       </c>
     </row>
     <row r="390">
@@ -5294,7 +5288,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-1.24625951908067</v>
+        <v>-0.836006160817576</v>
       </c>
     </row>
     <row r="391">
@@ -5305,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.42814282722071</v>
+        <v>-0.247409222256924</v>
       </c>
     </row>
     <row r="392">
@@ -5327,7 +5321,7 @@
         <v>16</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.184101770870354</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="394">
@@ -5349,7 +5343,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>0.55703410337875</v>
+        <v>0.5422265995104</v>
       </c>
     </row>
     <row r="396">
@@ -5371,7 +5365,7 @@
         <v>16</v>
       </c>
       <c r="C397" t="n">
-        <v>0.0878098101464756</v>
+        <v>-0.175280884462258</v>
       </c>
     </row>
     <row r="398">
@@ -5382,7 +5376,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-0.323739226607421</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="399">
@@ -5415,7 +5409,7 @@
         <v>16</v>
       </c>
       <c r="C401" t="n">
-        <v>-0.144818943006015</v>
+        <v>-0.163814921372418</v>
       </c>
     </row>
     <row r="402">
@@ -5448,7 +5442,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.278699100289377</v>
+        <v>-0.201224884939716</v>
       </c>
     </row>
     <row r="405">
@@ -5459,7 +5453,7 @@
         <v>16</v>
       </c>
       <c r="C405" t="n">
-        <v>-0.173268790027109</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="406">
@@ -5470,7 +5464,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>0.0248522762928728</v>
+        <v>-0.134394018475023</v>
       </c>
     </row>
     <row r="407">
@@ -5492,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>-0.193640691719475</v>
+        <v>-0.185757537984083</v>
       </c>
     </row>
     <row r="409">
@@ -5503,7 +5497,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="n">
-        <v>-0.40856407642647</v>
+        <v>-0.259622816826455</v>
       </c>
     </row>
     <row r="410">
@@ -5525,7 +5519,7 @@
         <v>16</v>
       </c>
       <c r="C411" t="n">
-        <v>-0.589927462730188</v>
+        <v>-0.39558286292498</v>
       </c>
     </row>
     <row r="412">
@@ -5580,7 +5574,7 @@
         <v>16</v>
       </c>
       <c r="C416" t="n">
-        <v>-0.449182642562524</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="417">
@@ -5591,7 +5585,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-1.65186787441292</v>
+        <v>-0.621725645519436</v>
       </c>
     </row>
     <row r="418">
@@ -5613,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.373660052130421</v>
+        <v>-0.404173210152553</v>
       </c>
     </row>
     <row r="420">
@@ -5624,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>-0.103106278970512</v>
+        <v>-0.215797609002959</v>
       </c>
     </row>
     <row r="421">
@@ -5690,7 +5684,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>-0.0492194395668863</v>
+        <v>-0.119428797757354</v>
       </c>
     </row>
     <row r="427">
@@ -5723,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.263081742698248</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="430">
@@ -5756,7 +5750,7 @@
         <v>16</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.207943746341251</v>
+        <v>-0.220229727465034</v>
       </c>
     </row>
     <row r="433">
@@ -5778,7 +5772,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.213099052862316</v>
+        <v>-0.17222099389843</v>
       </c>
     </row>
     <row r="435">
@@ -5811,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>-0.208050805318725</v>
+        <v>-0.506470115870334</v>
       </c>
     </row>
     <row r="438">
@@ -5844,7 +5838,7 @@
         <v>16</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.852359179178732</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="441">
@@ -5855,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.39586789519611</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="442">
@@ -5866,7 +5860,7 @@
         <v>16</v>
       </c>
       <c r="C442" t="n">
-        <v>-0.377775752656908</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="443">
@@ -5877,7 +5871,7 @@
         <v>16</v>
       </c>
       <c r="C443" t="n">
-        <v>-0.476798982658161</v>
+        <v>-0.226303840511765</v>
       </c>
     </row>
     <row r="444">
@@ -5899,7 +5893,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.14790436655734</v>
       </c>
     </row>
     <row r="446">
@@ -5932,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="C448" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.163708783081168</v>
       </c>
     </row>
     <row r="449">
@@ -5943,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.158097322985582</v>
+        <v>-0.31547362465993</v>
       </c>
     </row>
     <row r="450">
@@ -5965,7 +5959,7 @@
         <v>16</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.26277962171327</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="452">
@@ -5976,7 +5970,7 @@
         <v>16</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.220833226615046</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="453">
@@ -5987,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>-0.221690123624659</v>
+        <v>-0.213447502905471</v>
       </c>
     </row>
     <row r="454">
@@ -5998,7 +5992,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.520936979357726</v>
       </c>
     </row>
     <row r="455">
@@ -6020,7 +6014,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.511707789257158</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="457">
@@ -6031,7 +6025,7 @@
         <v>16</v>
       </c>
       <c r="C457" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.236450334457395</v>
       </c>
     </row>
     <row r="458">
@@ -6097,7 +6091,7 @@
         <v>16</v>
       </c>
       <c r="C463" t="n">
-        <v>-0.452111515244177</v>
+        <v>-0.391394788311818</v>
       </c>
     </row>
     <row r="464">
@@ -6119,7 +6113,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.155285620394</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="466">
@@ -6130,7 +6124,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.250351074762264</v>
+        <v>-0.20106210858636</v>
       </c>
     </row>
     <row r="467">
@@ -6152,7 +6146,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.294253244164579</v>
+        <v>-0.222269530844729</v>
       </c>
     </row>
     <row r="469">
@@ -6163,7 +6157,7 @@
         <v>16</v>
       </c>
       <c r="C469" t="n">
-        <v>-0.333010470082391</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="470">
@@ -6174,7 +6168,7 @@
         <v>16</v>
       </c>
       <c r="C470" t="n">
-        <v>-0.126885475883715</v>
+        <v>-0.147305828669522</v>
       </c>
     </row>
     <row r="471">
@@ -6185,7 +6179,7 @@
         <v>16</v>
       </c>
       <c r="C471" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.980691456175805</v>
       </c>
     </row>
     <row r="472">
@@ -6207,7 +6201,7 @@
         <v>16</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.299964704964332</v>
+        <v>-0.312235977286776</v>
       </c>
     </row>
     <row r="474">
@@ -6218,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>0.1970061135823</v>
+        <v>-0.238205610283243</v>
       </c>
     </row>
     <row r="475">
@@ -6229,7 +6223,7 @@
         <v>16</v>
       </c>
       <c r="C475" t="n">
-        <v>0.00683760075122164</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="476">
@@ -6251,7 +6245,7 @@
         <v>16</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.149109475841504</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="478">
@@ -6262,7 +6256,7 @@
         <v>16</v>
       </c>
       <c r="C478" t="n">
-        <v>-0.393845120958749</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="479">
@@ -6273,7 +6267,7 @@
         <v>16</v>
       </c>
       <c r="C479" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.427068808012913</v>
       </c>
     </row>
     <row r="480">
@@ -6295,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>0.356927141066066</v>
+        <v>0.0215741644410256</v>
       </c>
     </row>
     <row r="482">
@@ -6306,7 +6300,7 @@
         <v>16</v>
       </c>
       <c r="C482" t="n">
-        <v>-0.150912243157489</v>
+        <v>0.454683260437351</v>
       </c>
     </row>
     <row r="483">
@@ -6350,7 +6344,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.166482579241467</v>
+        <v>-0.170225858119477</v>
       </c>
     </row>
     <row r="487">
@@ -6361,7 +6355,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.3851805364343</v>
+        <v>-0.322319458700433</v>
       </c>
     </row>
     <row r="488">
@@ -6372,7 +6366,7 @@
         <v>16</v>
       </c>
       <c r="C488" t="n">
-        <v>-0.430255695862808</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="489">
@@ -6383,7 +6377,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.238206398359717</v>
+        <v>-0.182246242099346</v>
       </c>
     </row>
     <row r="490">
@@ -6394,7 +6388,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-0.113970663476847</v>
+        <v>0.0461413222144731</v>
       </c>
     </row>
     <row r="491">
@@ -6427,7 +6421,7 @@
         <v>16</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.0125180060484444</v>
+        <v>-0.156958785794796</v>
       </c>
     </row>
     <row r="494">
@@ -6449,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.36914416741526</v>
       </c>
     </row>
     <row r="496">
@@ -6460,7 +6454,7 @@
         <v>16</v>
       </c>
       <c r="C496" t="n">
-        <v>0.320182438410355</v>
+        <v>0.191556589465251</v>
       </c>
     </row>
     <row r="497">
@@ -6493,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>0.234714814008696</v>
+        <v>0.0292842778482567</v>
       </c>
     </row>
     <row r="500">
@@ -6504,7 +6498,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>0.285292450886878</v>
+        <v>-0.0531627087950406</v>
       </c>
     </row>
     <row r="501">
@@ -6548,7 +6542,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.19701830910825</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="505">
@@ -6559,7 +6553,7 @@
         <v>16</v>
       </c>
       <c r="C505" t="n">
-        <v>-0.192795694993685</v>
+        <v>-0.172894309209487</v>
       </c>
     </row>
     <row r="506">
@@ -6603,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.331571959027197</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="510">
@@ -6636,7 +6630,7 @@
         <v>16</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.391743617930275</v>
+        <v>-0.245276699992198</v>
       </c>
     </row>
     <row r="513">
@@ -6647,7 +6641,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.183115220531896</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="514">
@@ -6658,7 +6652,7 @@
         <v>16</v>
       </c>
       <c r="C514" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.227547053264615</v>
       </c>
     </row>
     <row r="515">
@@ -6669,7 +6663,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.375619598378151</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="516">
@@ -6680,7 +6674,7 @@
         <v>16</v>
       </c>
       <c r="C516" t="n">
-        <v>-0.124932516716941</v>
+        <v>-0.150292629808618</v>
       </c>
     </row>
     <row r="517">
@@ -6691,7 +6685,7 @@
         <v>16</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.302775654984943</v>
+        <v>-0.338085574083982</v>
       </c>
     </row>
     <row r="518">
@@ -6702,7 +6696,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-1.10718838264647</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="519">
@@ -6713,7 +6707,7 @@
         <v>16</v>
       </c>
       <c r="C519" t="n">
-        <v>-0.750621261435636</v>
+        <v>-0.679027559880335</v>
       </c>
     </row>
     <row r="520">
@@ -6735,7 +6729,7 @@
         <v>16</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.167177001358855</v>
       </c>
     </row>
     <row r="522">
@@ -6768,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.34352676765893</v>
+        <v>-0.48067289401466</v>
       </c>
     </row>
     <row r="525">
@@ -6801,7 +6795,7 @@
         <v>16</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.260539062170988</v>
+        <v>-0.185532466862763</v>
       </c>
     </row>
     <row r="528">
@@ -6812,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.437129014564025</v>
+        <v>-0.280580966623507</v>
       </c>
     </row>
     <row r="529">
@@ -6845,7 +6839,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.372470479255222</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="532">
@@ -6856,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.375198026377099</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="533">
@@ -6867,7 +6861,7 @@
         <v>16</v>
       </c>
       <c r="C533" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.257970991960235</v>
       </c>
     </row>
     <row r="534">
@@ -6889,7 +6883,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.234889111906985</v>
+        <v>-0.159836043479331</v>
       </c>
     </row>
     <row r="536">
@@ -6900,7 +6894,7 @@
         <v>16</v>
       </c>
       <c r="C536" t="n">
-        <v>-0.228158309180013</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="537">
@@ -6911,7 +6905,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.446230208834367</v>
+        <v>-0.735484635812855</v>
       </c>
     </row>
     <row r="538">
@@ -6922,7 +6916,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.300860849078674</v>
+        <v>-0.34359501117693</v>
       </c>
     </row>
     <row r="539">
@@ -6933,7 +6927,7 @@
         <v>16</v>
       </c>
       <c r="C539" t="n">
-        <v>-0.604485982739444</v>
+        <v>-0.329099062324493</v>
       </c>
     </row>
     <row r="540">
@@ -6944,7 +6938,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.259738867756911</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="541">
@@ -6955,7 +6949,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.159983424199207</v>
+        <v>-0.185201368655735</v>
       </c>
     </row>
     <row r="542">
@@ -6988,7 +6982,7 @@
         <v>16</v>
       </c>
       <c r="C544" t="n">
-        <v>0.188632201946491</v>
+        <v>0.388778848632106</v>
       </c>
     </row>
     <row r="545">
@@ -6999,7 +6993,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.257241345972191</v>
+        <v>-0.36143707575614</v>
       </c>
     </row>
     <row r="546">
@@ -7054,7 +7048,7 @@
         <v>16</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.296382504022118</v>
+        <v>-0.28651669716084</v>
       </c>
     </row>
     <row r="551">
@@ -7076,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.163372869774948</v>
+        <v>-0.112073053494506</v>
       </c>
     </row>
     <row r="553">
@@ -7120,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>0.461387931932702</v>
+        <v>0.291016180437778</v>
       </c>
     </row>
     <row r="557">
@@ -7131,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.199290573704297</v>
+        <v>-0.232198138020203</v>
       </c>
     </row>
     <row r="558">
@@ -7142,7 +7136,7 @@
         <v>16</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.0956612550740503</v>
+        <v>-0.415999134272561</v>
       </c>
     </row>
     <row r="559">
@@ -7153,7 +7147,7 @@
         <v>16</v>
       </c>
       <c r="C559" t="n">
-        <v>-0.165718580965754</v>
+        <v>-0.163448454155417</v>
       </c>
     </row>
     <row r="560">
@@ -7175,7 +7169,7 @@
         <v>16</v>
       </c>
       <c r="C561" t="n">
-        <v>-0.19242820209391</v>
+        <v>-0.214376766208924</v>
       </c>
     </row>
     <row r="562">
@@ -7197,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.340743022538917</v>
+        <v>-0.316181144585437</v>
       </c>
     </row>
     <row r="564">
@@ -7219,7 +7213,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.149594707365417</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="566">
@@ -7274,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.544854061930999</v>
+        <v>-0.48721862978818</v>
       </c>
     </row>
     <row r="571">
@@ -7307,7 +7301,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.239429800134474</v>
       </c>
     </row>
     <row r="574">
@@ -7318,7 +7312,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.193256415833458</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="575">
@@ -7329,7 +7323,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.289046222742505</v>
+        <v>-0.248727235155383</v>
       </c>
     </row>
     <row r="576">
@@ -7373,7 +7367,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.317888001980097</v>
+        <v>-0.179966812725675</v>
       </c>
     </row>
     <row r="580">
@@ -7384,7 +7378,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>0.0611660679581993</v>
+        <v>-0.178678903037499</v>
       </c>
     </row>
     <row r="581">
@@ -7406,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.148325349732465</v>
+        <v>-0.267949677456038</v>
       </c>
     </row>
     <row r="583">
@@ -7428,7 +7422,7 @@
         <v>16</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.241484345694421</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="585">
@@ -7439,7 +7433,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.191538633287808</v>
+        <v>-0.169548158441226</v>
       </c>
     </row>
     <row r="586">
@@ -7450,7 +7444,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.324766515211845</v>
+        <v>-0.222148563758989</v>
       </c>
     </row>
     <row r="587">
@@ -7461,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.202528667126519</v>
+        <v>-0.285557121917915</v>
       </c>
     </row>
     <row r="588">
@@ -7483,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.307850153144423</v>
+        <v>-0.299906948829083</v>
       </c>
     </row>
     <row r="590">
@@ -7494,7 +7488,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.734225016214002</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="591">
@@ -7516,7 +7510,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.20191416620591</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="593">
@@ -7549,7 +7543,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>0.224030792456867</v>
+        <v>0.420441698599463</v>
       </c>
     </row>
     <row r="596">
@@ -7571,7 +7565,7 @@
         <v>16</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.360051634774848</v>
+        <v>-0.329785384097217</v>
       </c>
     </row>
     <row r="598">
@@ -7582,7 +7576,7 @@
         <v>16</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.17564036323378</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="599">
@@ -7615,7 +7609,7 @@
         <v>16</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.183721737692011</v>
+        <v>-0.169220200680345</v>
       </c>
     </row>
     <row r="602">
@@ -7659,7 +7653,7 @@
         <v>16</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.239909051541852</v>
+        <v>-0.193275573828651</v>
       </c>
     </row>
     <row r="606">
@@ -7681,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.176784100319291</v>
+        <v>-0.189884019277029</v>
       </c>
     </row>
     <row r="608">
@@ -7692,7 +7686,7 @@
         <v>16</v>
       </c>
       <c r="C608" t="n">
-        <v>-0.418526094735788</v>
+        <v>-0.355893732877406</v>
       </c>
     </row>
     <row r="609">
@@ -7714,7 +7708,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.175511753741677</v>
+        <v>-0.264969919844429</v>
       </c>
     </row>
     <row r="611">
@@ -7736,7 +7730,7 @@
         <v>16</v>
       </c>
       <c r="C612" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.268448540653022</v>
       </c>
     </row>
     <row r="613">
@@ -7758,7 +7752,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.521410147303272</v>
       </c>
     </row>
     <row r="615">
@@ -7769,7 +7763,7 @@
         <v>16</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.100297231586093</v>
+        <v>-0.0393097773890734</v>
       </c>
     </row>
     <row r="616">
@@ -7802,7 +7796,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.276750667278298</v>
+        <v>-0.137102411062471</v>
       </c>
     </row>
     <row r="619">
@@ -7846,7 +7840,7 @@
         <v>16</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.177385475045798</v>
+        <v>-0.211359200693679</v>
       </c>
     </row>
     <row r="623">
@@ -7857,7 +7851,7 @@
         <v>16</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.202243364084521</v>
+        <v>-0.276235748959719</v>
       </c>
     </row>
     <row r="624">
@@ -7868,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>0.0261178680087354</v>
+        <v>-0.19014729772998</v>
       </c>
     </row>
     <row r="625">
@@ -7890,7 +7884,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.157210100500464</v>
+        <v>-0.201365365377279</v>
       </c>
     </row>
     <row r="627">
@@ -7923,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.111910564423032</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="630">
@@ -7934,7 +7928,7 @@
         <v>16</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.217005511065834</v>
+        <v>-0.385191841569165</v>
       </c>
     </row>
     <row r="631">
@@ -7956,7 +7950,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.147890851433351</v>
+        <v>-0.148876169697846</v>
       </c>
     </row>
     <row r="633">
@@ -7978,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.23289446900175</v>
+        <v>-0.31147271698228</v>
       </c>
     </row>
     <row r="635">
@@ -7989,7 +7983,7 @@
         <v>16</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.233092415367339</v>
       </c>
     </row>
     <row r="636">
@@ -8000,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>0.0568447738135159</v>
+        <v>0.0326130009109153</v>
       </c>
     </row>
     <row r="637">
@@ -8011,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.147317818581954</v>
       </c>
     </row>
     <row r="638">
@@ -8033,7 +8027,7 @@
         <v>16</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.127640413720685</v>
+        <v>0.0396198092306871</v>
       </c>
     </row>
     <row r="640">
@@ -8044,7 +8038,7 @@
         <v>16</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.258277993183434</v>
+        <v>-0.330770739345866</v>
       </c>
     </row>
     <row r="641">
@@ -8077,7 +8071,7 @@
         <v>16</v>
       </c>
       <c r="C643" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.31956042867352</v>
       </c>
     </row>
     <row r="644">
@@ -8088,7 +8082,7 @@
         <v>16</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.239751275640423</v>
+        <v>-0.300697707401375</v>
       </c>
     </row>
     <row r="645">
@@ -8099,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.0500649412033163</v>
+        <v>-0.158371083182689</v>
       </c>
     </row>
     <row r="646">
@@ -8110,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.182167424289512</v>
+        <v>-0.15829404218754</v>
       </c>
     </row>
     <row r="647">
@@ -8121,7 +8115,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>0.641366153806418</v>
+        <v>0.0343288125780057</v>
       </c>
     </row>
     <row r="648">
@@ -8132,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.0219644512427419</v>
+        <v>0.295115018666102</v>
       </c>
     </row>
     <row r="649">
@@ -8154,7 +8148,7 @@
         <v>16</v>
       </c>
       <c r="C650" t="n">
-        <v>0.198585315108724</v>
+        <v>0.244262727200142</v>
       </c>
     </row>
     <row r="651">
@@ -8165,7 +8159,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.156240453500551</v>
+        <v>-0.0598638210262659</v>
       </c>
     </row>
     <row r="652">
@@ -8187,7 +8181,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.640084499887035</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="654">
@@ -8209,7 +8203,7 @@
         <v>16</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.417121767909835</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="656">
@@ -8242,7 +8236,7 @@
         <v>16</v>
       </c>
       <c r="C658" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.148531661426809</v>
       </c>
     </row>
     <row r="659">
@@ -8275,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.130316966448274</v>
       </c>
     </row>
     <row r="662">
@@ -8286,7 +8280,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.144438905625548</v>
+        <v>-0.111258418017488</v>
       </c>
     </row>
     <row r="663">
@@ -8308,7 +8302,7 @@
         <v>16</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.280195781385204</v>
+        <v>-0.224383350114717</v>
       </c>
     </row>
     <row r="665">
@@ -8319,7 +8313,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.202319659742858</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="666">
@@ -8330,7 +8324,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.696665676060516</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="667">
@@ -8396,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.167721098084671</v>
+        <v>-0.219819787503214</v>
       </c>
     </row>
     <row r="673">
@@ -8407,7 +8401,7 @@
         <v>16</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.218823239888</v>
+        <v>-0.316463940632775</v>
       </c>
     </row>
     <row r="674">
@@ -8418,7 +8412,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.324579006625963</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="675">
@@ -8429,7 +8423,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.169838796883129</v>
+        <v>-0.169065012146188</v>
       </c>
     </row>
     <row r="676">
@@ -8473,7 +8467,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.592153463363397</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="680">
@@ -8495,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.229936081424513</v>
+        <v>-0.213674126683411</v>
       </c>
     </row>
     <row r="682">
@@ -8539,7 +8533,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>0.453044954076302</v>
+        <v>0.202818002220836</v>
       </c>
     </row>
     <row r="686">
@@ -8605,7 +8599,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.499209448558076</v>
+        <v>-0.576599274845473</v>
       </c>
     </row>
     <row r="692">
@@ -8616,7 +8610,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.30214241630112</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="693">
@@ -8638,7 +8632,7 @@
         <v>16</v>
       </c>
       <c r="C694" t="n">
-        <v>0.294170974457217</v>
+        <v>-0.378755125460467</v>
       </c>
     </row>
     <row r="695">
@@ -8671,7 +8665,7 @@
         <v>16</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.148337189817639</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="698">
@@ -8682,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.203360676153729</v>
+        <v>-0.199014526771365</v>
       </c>
     </row>
     <row r="699">
@@ -8704,7 +8698,7 @@
         <v>16</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.165519193143749</v>
+        <v>-0.145952468152616</v>
       </c>
     </row>
     <row r="701">
@@ -8715,7 +8709,7 @@
         <v>16</v>
       </c>
       <c r="C701" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.168537635622194</v>
       </c>
     </row>
     <row r="702">
@@ -8726,7 +8720,7 @@
         <v>16</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.173932045671086</v>
+        <v>-0.176048767637595</v>
       </c>
     </row>
     <row r="703">
@@ -8737,7 +8731,7 @@
         <v>16</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.374188360474514</v>
       </c>
     </row>
     <row r="704">
@@ -8770,7 +8764,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.188172157620131</v>
+        <v>-0.184920184236373</v>
       </c>
     </row>
     <row r="707">
@@ -8781,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.179494315410416</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="708">
@@ -8814,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.250679321797608</v>
+        <v>-0.163534339260043</v>
       </c>
     </row>
     <row r="711">
@@ -8902,7 +8896,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.150608705051541</v>
+        <v>-0.261062849049327</v>
       </c>
     </row>
     <row r="719">
@@ -8913,7 +8907,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>0.117099205735243</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="720">
@@ -8935,7 +8929,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>0.224721772820268</v>
+        <v>0.212622285312374</v>
       </c>
     </row>
     <row r="722">
@@ -8946,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.212348602263766</v>
       </c>
     </row>
     <row r="723">
@@ -8957,7 +8951,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.406648667959126</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="724">
@@ -8979,7 +8973,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.162376628661455</v>
+        <v>-0.152816229895906</v>
       </c>
     </row>
     <row r="726">
@@ -9001,7 +8995,7 @@
         <v>16</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.353154054694698</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="728">
@@ -9012,7 +9006,7 @@
         <v>16</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.125117355825057</v>
+        <v>-0.154486179209756</v>
       </c>
     </row>
     <row r="729">
@@ -9023,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>0.212291961737953</v>
+        <v>-0.206528050241448</v>
       </c>
     </row>
     <row r="730">
@@ -9034,7 +9028,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.187422163847496</v>
+        <v>0.0532303987683092</v>
       </c>
     </row>
     <row r="731">
@@ -9045,7 +9039,7 @@
         <v>16</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.624263858465592</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="732">
@@ -9056,7 +9050,7 @@
         <v>16</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.169219367624603</v>
+        <v>-0.189252523518117</v>
       </c>
     </row>
     <row r="733">
@@ -9067,7 +9061,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.590379104197394</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="734">
@@ -9089,7 +9083,7 @@
         <v>16</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.161139832257638</v>
+        <v>-0.167309532909609</v>
       </c>
     </row>
     <row r="736">
@@ -9100,7 +9094,7 @@
         <v>16</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.1792170899126</v>
+        <v>-0.187983647084369</v>
       </c>
     </row>
     <row r="737">
@@ -9133,7 +9127,7 @@
         <v>16</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.188353726253629</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="740">
@@ -9144,7 +9138,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.258646295379622</v>
       </c>
     </row>
     <row r="741">
@@ -9210,7 +9204,7 @@
         <v>16</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.270892569015955</v>
       </c>
     </row>
     <row r="747">
@@ -9232,7 +9226,7 @@
         <v>16</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.0197253259574885</v>
+        <v>0.0927031150848583</v>
       </c>
     </row>
     <row r="749">
@@ -9265,7 +9259,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.66897539266681</v>
+        <v>-0.0137831555672436</v>
       </c>
     </row>
     <row r="752">
@@ -9309,7 +9303,7 @@
         <v>16</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.169792930753375</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="756">
@@ -9320,7 +9314,7 @@
         <v>16</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.198610736502307</v>
+        <v>-0.190116052710593</v>
       </c>
     </row>
     <row r="757">
@@ -9353,7 +9347,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.189005704142428</v>
       </c>
     </row>
     <row r="760">
@@ -9364,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.251048728155427</v>
+        <v>-0.161217440844348</v>
       </c>
     </row>
     <row r="761">
@@ -9375,7 +9369,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.570792535866862</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="762">
@@ -9386,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.216363323567111</v>
+        <v>-0.156015231989192</v>
       </c>
     </row>
     <row r="763">
@@ -9408,7 +9402,7 @@
         <v>16</v>
       </c>
       <c r="C764" t="n">
-        <v>0.113816825128</v>
+        <v>0.19624104432873</v>
       </c>
     </row>
     <row r="765">
@@ -9419,7 +9413,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.148958249468342</v>
+        <v>-0.117021616470734</v>
       </c>
     </row>
     <row r="766">
@@ -9463,7 +9457,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.198991558370787</v>
+        <v>-0.247078411441684</v>
       </c>
     </row>
     <row r="770">
@@ -9474,7 +9468,7 @@
         <v>16</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.186887535102847</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="771">
@@ -9496,7 +9490,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.193215299106052</v>
+        <v>-0.189543764042051</v>
       </c>
     </row>
     <row r="773">
@@ -9518,7 +9512,7 @@
         <v>16</v>
       </c>
       <c r="C774" t="n">
-        <v>-0.172153314803284</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="775">
@@ -9551,7 +9545,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.503215436771817</v>
+        <v>-0.215726324940128</v>
       </c>
     </row>
     <row r="778">
@@ -9562,7 +9556,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.202395745126272</v>
+        <v>-0.224378167519911</v>
       </c>
     </row>
     <row r="779">
@@ -9573,7 +9567,7 @@
         <v>16</v>
       </c>
       <c r="C779" t="n">
-        <v>-0.333659094821786</v>
+        <v>-0.170330480592306</v>
       </c>
     </row>
     <row r="780">
@@ -9584,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.180714069811361</v>
+        <v>-0.211174857384319</v>
       </c>
     </row>
     <row r="781">
@@ -9595,7 +9589,7 @@
         <v>16</v>
       </c>
       <c r="C781" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.150794384517966</v>
       </c>
     </row>
     <row r="782">
@@ -9606,7 +9600,7 @@
         <v>16</v>
       </c>
       <c r="C782" t="n">
-        <v>0.0699519706701451</v>
+        <v>-0.0848666757963676</v>
       </c>
     </row>
     <row r="783">
@@ -9628,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.16944489883828</v>
+        <v>-0.240827203933989</v>
       </c>
     </row>
     <row r="785">
@@ -9650,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.148718515891125</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="787">
@@ -9661,7 +9655,7 @@
         <v>16</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.324971861048843</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="788">
@@ -9683,7 +9677,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.151246290235543</v>
+        <v>-0.156545253135646</v>
       </c>
     </row>
     <row r="790">
@@ -9694,7 +9688,7 @@
         <v>16</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.149864588177011</v>
       </c>
     </row>
     <row r="791">
@@ -9716,7 +9710,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.218915553652957</v>
+        <v>-0.194368009382266</v>
       </c>
     </row>
     <row r="793">
@@ -9760,7 +9754,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.209788389874289</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="797">
@@ -9771,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.2095057009119</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="798">
@@ -9782,7 +9776,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.583779418326478</v>
+        <v>-0.465497090636156</v>
       </c>
     </row>
     <row r="799">
@@ -9793,7 +9787,7 @@
         <v>16</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.430388764912367</v>
       </c>
     </row>
     <row r="800">
@@ -9815,7 +9809,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.835323351304275</v>
+        <v>-0.318524214351312</v>
       </c>
     </row>
     <row r="802">
@@ -9848,7 +9842,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.205090192626618</v>
       </c>
     </row>
     <row r="805">
@@ -9892,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.458882795117542</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="809">
@@ -9903,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>0.253244381396454</v>
+        <v>-0.324115241796994</v>
       </c>
     </row>
     <row r="810">
@@ -9991,7 +9985,7 @@
         <v>16</v>
       </c>
       <c r="C817" t="n">
-        <v>-0.260241958388346</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="818">
@@ -10002,7 +9996,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.160270441546209</v>
+        <v>-0.200164178963423</v>
       </c>
     </row>
     <row r="819">
@@ -10024,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.164059896302827</v>
+        <v>-0.230628893048228</v>
       </c>
     </row>
     <row r="821">
@@ -10046,7 +10040,7 @@
         <v>16</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.322749658501214</v>
       </c>
     </row>
     <row r="823">
@@ -10057,7 +10051,7 @@
         <v>16</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.15120898613368</v>
       </c>
     </row>
     <row r="824">
@@ -10079,7 +10073,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.50710494991547</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="826">
@@ -10101,7 +10095,7 @@
         <v>16</v>
       </c>
       <c r="C827" t="n">
-        <v>0.03375292286443</v>
+        <v>-0.278980648586954</v>
       </c>
     </row>
     <row r="828">
@@ -10112,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.329095607909922</v>
+        <v>-0.397046720872389</v>
       </c>
     </row>
     <row r="829">
@@ -10123,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.196232833931768</v>
       </c>
     </row>
     <row r="830">
@@ -10134,7 +10128,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.150855204981778</v>
+        <v>-0.208515685936385</v>
       </c>
     </row>
     <row r="831">
@@ -10145,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.396237906153749</v>
       </c>
     </row>
     <row r="832">
@@ -10167,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.282523521838357</v>
+        <v>-0.375912423800657</v>
       </c>
     </row>
     <row r="834">
@@ -10189,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.286006209039545</v>
+        <v>-0.196958198232736</v>
       </c>
     </row>
     <row r="836">
@@ -10200,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.169592307873694</v>
       </c>
     </row>
     <row r="837">
@@ -10211,7 +10205,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.548013566310071</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="838">
@@ -10222,7 +10216,7 @@
         <v>16</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.22338790056847</v>
+        <v>-0.229185722545937</v>
       </c>
     </row>
     <row r="839">
@@ -10233,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.216666590547181</v>
+        <v>-0.227621181089309</v>
       </c>
     </row>
     <row r="840">
@@ -10277,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.244398132921364</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="844">
@@ -10310,7 +10304,7 @@
         <v>16</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.203360730077375</v>
       </c>
     </row>
     <row r="847">
@@ -10354,7 +10348,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.20610506623861</v>
       </c>
     </row>
     <row r="851">
@@ -10365,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.36512449557957</v>
+        <v>-0.275763232201256</v>
       </c>
     </row>
     <row r="852">
@@ -10376,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.217399512108595</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="853">
@@ -10398,7 +10392,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.322558572215438</v>
+        <v>-0.532327670079057</v>
       </c>
     </row>
     <row r="855">
@@ -10420,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.172327435628173</v>
       </c>
     </row>
     <row r="857">
@@ -10431,7 +10425,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.240419214547175</v>
+        <v>-0.207145545385209</v>
       </c>
     </row>
     <row r="858">
@@ -10464,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.258982689540865</v>
+        <v>-0.13923031132015</v>
       </c>
     </row>
     <row r="861">
@@ -10497,7 +10491,7 @@
         <v>16</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.529047383335796</v>
+        <v>-0.383877888017931</v>
       </c>
     </row>
     <row r="864">
@@ -10541,7 +10535,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.309300774061142</v>
       </c>
     </row>
     <row r="868">
@@ -10552,7 +10546,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.341282631372261</v>
+        <v>-0.381227910760257</v>
       </c>
     </row>
     <row r="869">
@@ -10563,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.287814769900912</v>
+        <v>-0.306065847654498</v>
       </c>
     </row>
     <row r="870">
@@ -10585,7 +10579,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.268565169457451</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="872">
@@ -10596,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.626062039872707</v>
       </c>
     </row>
     <row r="873">
@@ -10640,7 +10634,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.274150067910177</v>
+        <v>-0.323249474098514</v>
       </c>
     </row>
     <row r="877">
@@ -10651,7 +10645,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.252899607373426</v>
+        <v>-0.171764126790906</v>
       </c>
     </row>
     <row r="878">
@@ -10673,7 +10667,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.335716388514249</v>
       </c>
     </row>
     <row r="880">
@@ -10684,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.102414395411781</v>
+        <v>-0.173273646113794</v>
       </c>
     </row>
     <row r="881">
@@ -10695,7 +10689,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.18964819596873</v>
+        <v>-0.38389356757368</v>
       </c>
     </row>
     <row r="882">
@@ -10728,7 +10722,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.206006974790685</v>
+        <v>-0.217748576450734</v>
       </c>
     </row>
     <row r="885">
@@ -10739,7 +10733,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.208462265726583</v>
+        <v>-0.205649829903473</v>
       </c>
     </row>
     <row r="886">
@@ -10750,7 +10744,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.413068440848108</v>
+        <v>-0.156007216323433</v>
       </c>
     </row>
     <row r="887">
@@ -10761,7 +10755,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.292968448009942</v>
+        <v>-0.258348270787505</v>
       </c>
     </row>
     <row r="888">
@@ -10783,7 +10777,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.315971723763141</v>
+        <v>-0.236928014776277</v>
       </c>
     </row>
     <row r="890">
@@ -10794,7 +10788,7 @@
         <v>16</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.216298069401568</v>
+        <v>-0.181950322383784</v>
       </c>
     </row>
     <row r="891">
@@ -10805,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.230009405017039</v>
       </c>
     </row>
     <row r="892">
@@ -10827,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>0.159562043906739</v>
+        <v>0.132361670716029</v>
       </c>
     </row>
     <row r="894">
@@ -10849,7 +10843,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.71953054577515</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="896">
@@ -10860,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>0.420051125971267</v>
+        <v>0.21085436026991</v>
       </c>
     </row>
     <row r="897">
@@ -10871,7 +10865,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.0912564082767815</v>
+        <v>-0.335526315944893</v>
       </c>
     </row>
     <row r="898">
@@ -10948,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.160490426525657</v>
+        <v>-0.189630118663971</v>
       </c>
     </row>
     <row r="905">
@@ -10981,7 +10975,7 @@
         <v>16</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.255667181234919</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="908">
@@ -10992,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.153506120160921</v>
+        <v>-0.230845247994207</v>
       </c>
     </row>
     <row r="909">
@@ -11025,7 +11019,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.661048156056267</v>
+        <v>-0.14898330979731</v>
       </c>
     </row>
     <row r="912">
@@ -11047,7 +11041,7 @@
         <v>16</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.211260882169786</v>
+        <v>-0.199744839391778</v>
       </c>
     </row>
     <row r="914">
@@ -11058,7 +11052,7 @@
         <v>16</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.171606151987266</v>
       </c>
     </row>
     <row r="915">
@@ -11069,7 +11063,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.164686116634495</v>
+        <v>-0.215537849486257</v>
       </c>
     </row>
     <row r="916">
@@ -11091,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.41925174009221</v>
+        <v>-0.186560281017544</v>
       </c>
     </row>
     <row r="918">
@@ -11102,7 +11096,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.154653425838485</v>
+        <v>-0.357136255820537</v>
       </c>
     </row>
     <row r="919">
@@ -11113,7 +11107,7 @@
         <v>16</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.17196168097189</v>
       </c>
     </row>
     <row r="920">
@@ -11168,7 +11162,7 @@
         <v>16</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.831429308338412</v>
       </c>
     </row>
     <row r="925">
@@ -11190,7 +11184,7 @@
         <v>16</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.230236140124834</v>
+        <v>-0.196245846360256</v>
       </c>
     </row>
     <row r="927">
@@ -11234,7 +11228,7 @@
         <v>16</v>
       </c>
       <c r="C930" t="n">
-        <v>-0.542241260909571</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="931">
@@ -11289,7 +11283,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.243998375572183</v>
+        <v>-0.158544943507146</v>
       </c>
     </row>
     <row r="936">
@@ -11311,7 +11305,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.0109152697333672</v>
+        <v>-0.091211051723578</v>
       </c>
     </row>
     <row r="938">
@@ -11322,7 +11316,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.149648040647393</v>
       </c>
     </row>
     <row r="939">
@@ -11344,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>0.0817813526396488</v>
+        <v>-0.27892323234337</v>
       </c>
     </row>
     <row r="941">
@@ -11355,7 +11349,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.245667195197191</v>
+        <v>-0.235982758153699</v>
       </c>
     </row>
     <row r="942">
@@ -11366,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.416520510449464</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="943">
@@ -11388,7 +11382,7 @@
         <v>16</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.172497441234085</v>
+        <v>-0.168568418308439</v>
       </c>
     </row>
     <row r="945">
@@ -11399,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.152880508515806</v>
+        <v>-0.173380321723716</v>
       </c>
     </row>
     <row r="946">
@@ -11421,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-0.320135028122675</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="948">
@@ -11443,7 +11437,7 @@
         <v>16</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.559966862158819</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="950">
@@ -11465,7 +11459,7 @@
         <v>16</v>
       </c>
       <c r="C951" t="n">
-        <v>0.0436896452065182</v>
+        <v>0.126272661727929</v>
       </c>
     </row>
     <row r="952">
@@ -11476,7 +11470,7 @@
         <v>16</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.261293863535543</v>
+        <v>-0.236154180980604</v>
       </c>
     </row>
     <row r="953">
@@ -11498,7 +11492,7 @@
         <v>16</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.446131360655182</v>
+        <v>-0.255478940727533</v>
       </c>
     </row>
     <row r="955">
@@ -11542,7 +11536,7 @@
         <v>16</v>
       </c>
       <c r="C958" t="n">
-        <v>0.340821077570077</v>
+        <v>-0.198849333920053</v>
       </c>
     </row>
     <row r="959">
@@ -11619,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.0170878152355278</v>
+        <v>0.076124198979333</v>
       </c>
     </row>
     <row r="966">
@@ -11630,7 +11624,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.283295312358468</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="967">
@@ -11674,7 +11668,7 @@
         <v>16</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.217835019293966</v>
       </c>
     </row>
     <row r="971">
@@ -11685,7 +11679,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.165407742864295</v>
+        <v>-0.268548043893335</v>
       </c>
     </row>
     <row r="972">
@@ -11751,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.269225202552628</v>
+        <v>0.122959097721157</v>
       </c>
     </row>
     <row r="978">
@@ -11762,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.177351504284154</v>
+        <v>-0.167174743428124</v>
       </c>
     </row>
     <row r="979">
@@ -11773,7 +11767,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-0.200578088531019</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="980">
@@ -11784,7 +11778,7 @@
         <v>16</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.360897759915311</v>
+        <v>-0.29086558062671</v>
       </c>
     </row>
     <row r="981">
@@ -11795,7 +11789,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.152040715110845</v>
       </c>
     </row>
     <row r="982">
@@ -11817,7 +11811,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.136892278687213</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="984">
@@ -11828,7 +11822,7 @@
         <v>16</v>
       </c>
       <c r="C984" t="n">
-        <v>-0.383068374681923</v>
+        <v>-0.229659012731259</v>
       </c>
     </row>
     <row r="985">
@@ -11839,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.292732971989823</v>
+        <v>-0.414058127057696</v>
       </c>
     </row>
     <row r="986">
@@ -11861,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.288573299503988</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="988">
@@ -11872,7 +11866,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.20603443007903</v>
+        <v>-0.194684722531442</v>
       </c>
     </row>
     <row r="989">
@@ -11883,7 +11877,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.28213903794409</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="990">
@@ -11894,7 +11888,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.371087960283742</v>
+        <v>-0.328516144887907</v>
       </c>
     </row>
     <row r="991">
@@ -11905,7 +11899,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.533231104597281</v>
       </c>
     </row>
     <row r="992">
@@ -11949,7 +11943,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.245838323431303</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="996">
@@ -11971,7 +11965,7 @@
         <v>16</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.289836606078774</v>
+        <v>-0.186553600015267</v>
       </c>
     </row>
     <row r="998">
@@ -11982,7 +11976,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.14973587685467</v>
+        <v>-0.164949721106528</v>
       </c>
     </row>
     <row r="999">
@@ -12103,7 +12097,7 @@
         <v>16</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.161258833269374</v>
       </c>
     </row>
     <row r="1010">
@@ -12125,7 +12119,7 @@
         <v>16</v>
       </c>
       <c r="C1011" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.204859013697486</v>
       </c>
     </row>
     <row r="1012">
@@ -12147,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.160897785818465</v>
+        <v>-0.406069212384704</v>
       </c>
     </row>
     <row r="1014">
@@ -12158,7 +12152,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.168123567406054</v>
       </c>
     </row>
     <row r="1015">
@@ -12169,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.39149039977016</v>
       </c>
     </row>
     <row r="1016">
@@ -12224,7 +12218,7 @@
         <v>16</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.207771198533138</v>
       </c>
     </row>
     <row r="1021">
@@ -12235,7 +12229,7 @@
         <v>16</v>
       </c>
       <c r="C1021" t="n">
-        <v>-0.165126745584265</v>
+        <v>-0.321675598982496</v>
       </c>
     </row>
     <row r="1022">
@@ -12246,7 +12240,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.18169932641012</v>
+        <v>-0.186737638388301</v>
       </c>
     </row>
     <row r="1023">
@@ -12257,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.649565846638781</v>
       </c>
     </row>
     <row r="1024">
@@ -12279,7 +12273,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.253555323589902</v>
       </c>
     </row>
     <row r="1026">
@@ -12290,7 +12284,7 @@
         <v>16</v>
       </c>
       <c r="C1026" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.328019369499808</v>
       </c>
     </row>
     <row r="1027">
@@ -12301,7 +12295,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.444854678634705</v>
       </c>
     </row>
     <row r="1028">
@@ -12312,7 +12306,7 @@
         <v>16</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.188266573570557</v>
       </c>
     </row>
     <row r="1029">
@@ -12334,7 +12328,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.170324355133286</v>
       </c>
     </row>
     <row r="1031">
@@ -12400,7 +12394,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.329740499214464</v>
       </c>
     </row>
     <row r="1037">
@@ -12444,7 +12438,7 @@
         <v>16</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.177345965869069</v>
+        <v>-0.369732481845569</v>
       </c>
     </row>
     <row r="1041">
@@ -12455,7 +12449,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.17118358591483</v>
       </c>
     </row>
     <row r="1042">
@@ -12466,7 +12460,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.255454678501513</v>
       </c>
     </row>
     <row r="1043">
@@ -12521,7 +12515,7 @@
         <v>16</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.203492284242759</v>
       </c>
     </row>
     <row r="1048">
@@ -12532,7 +12526,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.225431215501382</v>
       </c>
     </row>
     <row r="1049">
@@ -12543,7 +12537,7 @@
         <v>16</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.391424746499666</v>
       </c>
     </row>
     <row r="1050">
@@ -12554,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.162872091711874</v>
+        <v>-0.224296458471701</v>
       </c>
     </row>
     <row r="1051">
@@ -12565,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.323433231433912</v>
       </c>
     </row>
     <row r="1052">
@@ -12598,7 +12592,7 @@
         <v>16</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.550810129601809</v>
       </c>
     </row>
     <row r="1055">
@@ -12642,7 +12636,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.208900045607867</v>
       </c>
     </row>
     <row r="1059">
@@ -12653,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>-0.161868090454494</v>
+        <v>-0.115699078267584</v>
       </c>
     </row>
     <row r="1060">
@@ -12686,7 +12680,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.329577671425655</v>
       </c>
     </row>
     <row r="1063">
@@ -12697,7 +12691,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.181440408428692</v>
       </c>
     </row>
     <row r="1064">
@@ -12730,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.160852501880485</v>
+        <v>-0.326760622704017</v>
       </c>
     </row>
     <row r="1067">
@@ -12741,7 +12735,7 @@
         <v>16</v>
       </c>
       <c r="C1067" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.132257149372864</v>
       </c>
     </row>
     <row r="1068">
@@ -12752,7 +12746,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.194343882788155</v>
       </c>
     </row>
     <row r="1069">
@@ -12763,7 +12757,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.189581692592509</v>
       </c>
     </row>
     <row r="1070">
@@ -12807,7 +12801,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.164878447888152</v>
       </c>
     </row>
     <row r="1074">
@@ -12862,7 +12856,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.161249861211999</v>
       </c>
     </row>
     <row r="1079">
@@ -12906,7 +12900,7 @@
         <v>16</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.207551003858143</v>
       </c>
     </row>
     <row r="1083">
@@ -12928,7 +12922,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.172346199489936</v>
       </c>
     </row>
     <row r="1085">
@@ -12939,7 +12933,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.181503366563252</v>
       </c>
     </row>
     <row r="1086">
@@ -12950,7 +12944,7 @@
         <v>16</v>
       </c>
       <c r="C1086" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.543207501465077</v>
       </c>
     </row>
     <row r="1087">
@@ -12994,7 +12988,7 @@
         <v>16</v>
       </c>
       <c r="C1090" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.641750191679556</v>
       </c>
     </row>
     <row r="1091">
@@ -13016,7 +13010,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.166425212487056</v>
+        <v>-0.177025140909462</v>
       </c>
     </row>
     <row r="1093">
@@ -13027,7 +13021,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.169199259048852</v>
       </c>
     </row>
     <row r="1094">
@@ -13049,7 +13043,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.205618229055807</v>
       </c>
     </row>
     <row r="1096">
@@ -13093,7 +13087,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.19386464734343</v>
       </c>
     </row>
     <row r="1100">
@@ -13115,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.405508721460529</v>
       </c>
     </row>
     <row r="1102">
@@ -13137,7 +13131,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.272809015178519</v>
       </c>
     </row>
     <row r="1104">
@@ -13159,7 +13153,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.231187152515649</v>
       </c>
     </row>
     <row r="1106">
@@ -13214,7 +13208,7 @@
         <v>16</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.4211339294623</v>
       </c>
     </row>
     <row r="1111">
@@ -13236,7 +13230,7 @@
         <v>16</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.236913795350581</v>
       </c>
     </row>
     <row r="1113">
@@ -13247,7 +13241,7 @@
         <v>16</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.314756070304038</v>
       </c>
     </row>
     <row r="1114">
@@ -13269,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.311115792105799</v>
       </c>
     </row>
     <row r="1116">
@@ -13346,7 +13340,7 @@
         <v>16</v>
       </c>
       <c r="C1122" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.230637914847718</v>
       </c>
     </row>
     <row r="1123">
@@ -13401,7 +13395,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.151656840024182</v>
       </c>
     </row>
     <row r="1128">
@@ -13423,7 +13417,7 @@
         <v>16</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.281056734823625</v>
       </c>
     </row>
     <row r="1130">
@@ -13434,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.182933513287366</v>
       </c>
     </row>
     <row r="1131">
@@ -13566,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.167273419842022</v>
       </c>
     </row>
     <row r="1143">
@@ -13577,7 +13571,7 @@
         <v>16</v>
       </c>
       <c r="C1143" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.161414445945389</v>
       </c>
     </row>
     <row r="1144">
@@ -13588,7 +13582,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.18043187659699</v>
       </c>
     </row>
     <row r="1145">
@@ -13599,7 +13593,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.167646743632063</v>
       </c>
     </row>
     <row r="1146">
@@ -13610,7 +13604,7 @@
         <v>16</v>
       </c>
       <c r="C1146" t="n">
-        <v>-0.159282566758634</v>
+        <v>-0.0906174740727232</v>
       </c>
     </row>
     <row r="1147">
@@ -13632,7 +13626,7 @@
         <v>16</v>
       </c>
       <c r="C1148" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.214317130861599</v>
       </c>
     </row>
     <row r="1149">
@@ -13654,7 +13648,7 @@
         <v>16</v>
       </c>
       <c r="C1150" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.223623318618532</v>
       </c>
     </row>
     <row r="1151">
@@ -13665,7 +13659,7 @@
         <v>16</v>
       </c>
       <c r="C1151" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.261980871900236</v>
       </c>
     </row>
     <row r="1152">
@@ -13720,7 +13714,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.300261141062589</v>
       </c>
     </row>
     <row r="1157">
@@ -13753,7 +13747,7 @@
         <v>16</v>
       </c>
       <c r="C1159" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.500123146143562</v>
       </c>
     </row>
     <row r="1160">
@@ -13764,7 +13758,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.35940584048324</v>
       </c>
     </row>
     <row r="1161">
@@ -13775,7 +13769,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.0228731200788097</v>
       </c>
     </row>
     <row r="1162">
@@ -13786,7 +13780,7 @@
         <v>16</v>
       </c>
       <c r="C1162" t="n">
-        <v>-0.184571223336417</v>
+        <v>-0.163717855222717</v>
       </c>
     </row>
     <row r="1163">
@@ -13863,7 +13857,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.191926600054397</v>
+        <v>-0.251154055293043</v>
       </c>
     </row>
     <row r="1170">
@@ -13874,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.158372251096235</v>
       </c>
     </row>
     <row r="1171">
@@ -13885,7 +13879,7 @@
         <v>16</v>
       </c>
       <c r="C1171" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.265396686908697</v>
       </c>
     </row>
     <row r="1172">
@@ -13896,7 +13890,7 @@
         <v>16</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.150068499367344</v>
       </c>
     </row>
     <row r="1173">
@@ -13929,7 +13923,7 @@
         <v>16</v>
       </c>
       <c r="C1175" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.203532866976227</v>
       </c>
     </row>
     <row r="1176">
@@ -13940,7 +13934,7 @@
         <v>16</v>
       </c>
       <c r="C1176" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.358642739481217</v>
       </c>
     </row>
     <row r="1177">
@@ -13962,7 +13956,7 @@
         <v>16</v>
       </c>
       <c r="C1178" t="n">
-        <v>-0.184461838676105</v>
+        <v>-0.36820454563638</v>
       </c>
     </row>
     <row r="1179">
@@ -13984,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.163981082319158</v>
       </c>
     </row>
     <row r="1181">
@@ -13995,7 +13989,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.32848002662845</v>
       </c>
     </row>
     <row r="1182">
@@ -14028,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.16517650767404</v>
+        <v>0.334406369054724</v>
       </c>
     </row>
     <row r="1185">
@@ -14050,7 +14044,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.165769070166121</v>
       </c>
     </row>
     <row r="1187">
@@ -14072,7 +14066,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.235701525772833</v>
       </c>
     </row>
     <row r="1189">
@@ -14083,7 +14077,7 @@
         <v>16</v>
       </c>
       <c r="C1189" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.163661251965864</v>
       </c>
     </row>
     <row r="1190">
@@ -14127,7 +14121,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.20059652936768</v>
       </c>
     </row>
     <row r="1194">
@@ -14138,7 +14132,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.160451026189577</v>
+        <v>-0.0275364208129703</v>
       </c>
     </row>
     <row r="1195">
@@ -14204,7 +14198,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.100342083380131</v>
       </c>
     </row>
     <row r="1201">
@@ -15620,7 +15614,7 @@
         <v>8</v>
       </c>
       <c r="E82" t="n">
-        <v>8.92307692307692</v>
+        <v>9.23829364818843</v>
       </c>
     </row>
     <row r="83">
@@ -15739,7 +15733,7 @@
         <v>15</v>
       </c>
       <c r="E89" t="n">
-        <v>8.38461538461539</v>
+        <v>8.37859408938132</v>
       </c>
     </row>
     <row r="90">
@@ -15976,13 +15970,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>15</v>
@@ -15993,13 +15987,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>15</v>
@@ -16016,7 +16010,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>15</v>
@@ -16033,7 +16027,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>15</v>
@@ -16050,7 +16044,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
         <v>15</v>
@@ -16067,7 +16061,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
         <v>15</v>
@@ -16084,7 +16078,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -16101,7 +16095,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -16118,7 +16112,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" t="n">
         <v>15</v>
@@ -16135,7 +16129,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" t="n">
         <v>15</v>
@@ -16152,7 +16146,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D23" t="n">
         <v>15</v>
@@ -16163,13 +16157,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D24" t="n">
         <v>15</v>
@@ -16180,13 +16174,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D25" t="n">
         <v>15</v>
@@ -16197,13 +16191,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D26" t="n">
         <v>15</v>
@@ -16214,13 +16208,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D27" t="n">
         <v>15</v>
@@ -16237,7 +16231,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D28" t="n">
         <v>15</v>
@@ -16254,7 +16248,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D29" t="n">
         <v>15</v>
@@ -16271,7 +16265,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D30" t="n">
         <v>15</v>
@@ -16288,7 +16282,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D31" t="n">
         <v>15</v>
@@ -16305,7 +16299,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D32" t="n">
         <v>15</v>
@@ -16322,7 +16316,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D33" t="n">
         <v>15</v>
@@ -16339,7 +16333,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D34" t="n">
         <v>15</v>
@@ -16350,13 +16344,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D35" t="n">
         <v>15</v>
@@ -16367,13 +16361,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D36" t="n">
         <v>15</v>
@@ -16384,13 +16378,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D37" t="n">
         <v>15</v>
@@ -16401,13 +16395,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D38" t="n">
         <v>15</v>
@@ -16418,13 +16412,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D39" t="n">
         <v>15</v>
@@ -16435,13 +16429,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D40" t="n">
         <v>15</v>
@@ -16458,7 +16452,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D41" t="n">
         <v>15</v>
@@ -16475,7 +16469,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D42" t="n">
         <v>15</v>
@@ -16492,7 +16486,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D43" t="n">
         <v>15</v>
@@ -16509,7 +16503,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D44" t="n">
         <v>15</v>
@@ -16526,7 +16520,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D45" t="n">
         <v>15</v>
@@ -16537,13 +16531,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D46" t="n">
         <v>15</v>
@@ -16554,13 +16548,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D47" t="n">
         <v>15</v>
@@ -16571,13 +16565,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D48" t="n">
         <v>15</v>
@@ -16588,13 +16582,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D49" t="n">
         <v>15</v>
@@ -16605,13 +16599,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
         <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D50" t="n">
         <v>15</v>
@@ -16622,13 +16616,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D51" t="n">
         <v>15</v>
@@ -16639,13 +16633,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D52" t="n">
         <v>15</v>
@@ -16656,13 +16650,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B53" t="s">
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D53" t="n">
         <v>15</v>
@@ -16679,7 +16673,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D54" t="n">
         <v>15</v>
@@ -16696,7 +16690,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D55" t="n">
         <v>15</v>
@@ -16713,7 +16707,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D56" t="n">
         <v>15</v>
@@ -16724,16 +16718,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s">
         <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D57" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -16741,16 +16735,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -16758,16 +16752,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
         <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -16775,16 +16769,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -16792,16 +16786,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
         <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -16809,16 +16803,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
         <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D62" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -16826,16 +16820,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
         <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -16843,16 +16837,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
         <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D64" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -16860,16 +16854,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
         <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D65" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -16877,16 +16871,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
         <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D66" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -16900,216 +16894,12 @@
         <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D67" t="n">
         <v>14</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="s">
-        <v>44</v>
-      </c>
-      <c r="D68" t="n">
-        <v>14</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="s">
-        <v>45</v>
-      </c>
-      <c r="D69" t="n">
-        <v>14</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>21</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="s">
-        <v>46</v>
-      </c>
-      <c r="D70" t="n">
-        <v>14</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="s">
-        <v>47</v>
-      </c>
-      <c r="D71" t="n">
-        <v>14</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>21</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>48</v>
-      </c>
-      <c r="D72" t="n">
-        <v>14</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>21</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="s">
-        <v>49</v>
-      </c>
-      <c r="D73" t="n">
-        <v>14</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="s">
-        <v>50</v>
-      </c>
-      <c r="D74" t="n">
-        <v>14</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>21</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="s">
-        <v>51</v>
-      </c>
-      <c r="D75" t="n">
-        <v>14</v>
-      </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="s">
-        <v>52</v>
-      </c>
-      <c r="D76" t="n">
-        <v>14</v>
-      </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>21</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="s">
-        <v>53</v>
-      </c>
-      <c r="D77" t="n">
-        <v>14</v>
-      </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="s">
-        <v>54</v>
-      </c>
-      <c r="D78" t="n">
-        <v>14</v>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>21</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="s">
-        <v>55</v>
-      </c>
-      <c r="D79" t="n">
-        <v>14</v>
-      </c>
-      <c r="E79" t="n">
         <v>1</v>
       </c>
     </row>
